--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>85800</v>
+        <v>85300</v>
       </c>
       <c r="C419" t="n">
-        <v>171112</v>
+        <v>406686</v>
       </c>
       <c r="D419" t="n">
-        <v>91878</v>
+        <v>91789</v>
       </c>
       <c r="E419" t="n">
-        <v>88195</v>
+        <v>88105</v>
       </c>
       <c r="F419" t="n">
-        <v>86466</v>
+        <v>86179</v>
       </c>
       <c r="G419" t="n">
-        <v>88846</v>
+        <v>88691</v>
       </c>
       <c r="H419" t="n">
-        <v>0.2235213110238932</v>
+        <v>0.2213867658197342</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>0.2213867658197342</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>88200</v>
+      </c>
+      <c r="C420" t="n">
+        <v>257072</v>
+      </c>
+      <c r="D420" t="n">
+        <v>91334</v>
+      </c>
+      <c r="E420" t="n">
+        <v>87195</v>
+      </c>
+      <c r="F420" t="n">
+        <v>86334</v>
+      </c>
+      <c r="G420" t="n">
+        <v>88288</v>
+      </c>
+      <c r="H420" t="n">
+        <v>0.2158369482889211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>92000</v>
+        <v>90700</v>
       </c>
       <c r="C421" t="n">
-        <v>121712</v>
+        <v>427720</v>
       </c>
       <c r="D421" t="n">
-        <v>91147</v>
+        <v>91130</v>
       </c>
       <c r="E421" t="n">
-        <v>87291</v>
+        <v>87430</v>
       </c>
       <c r="F421" t="n">
-        <v>86817</v>
+        <v>87522</v>
       </c>
       <c r="G421" t="n">
-        <v>88418</v>
+        <v>88694</v>
       </c>
       <c r="H421" t="n">
-        <v>0.2176272120085381</v>
+        <v>0.2214280795978791</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>0.2214280795978791</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>91100</v>
+      </c>
+      <c r="C422" t="n">
+        <v>449809</v>
+      </c>
+      <c r="D422" t="n">
+        <v>90914</v>
+      </c>
+      <c r="E422" t="n">
+        <v>87672</v>
+      </c>
+      <c r="F422" t="n">
+        <v>88638</v>
+      </c>
+      <c r="G422" t="n">
+        <v>89075</v>
+      </c>
+      <c r="H422" t="n">
+        <v>0.2266749294222956</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>0.2266749294222956</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>88800</v>
+      </c>
+      <c r="C423" t="n">
+        <v>251051</v>
+      </c>
+      <c r="D423" t="n">
+        <v>90374</v>
+      </c>
+      <c r="E423" t="n">
+        <v>87700</v>
+      </c>
+      <c r="F423" t="n">
+        <v>88950</v>
+      </c>
+      <c r="G423" t="n">
+        <v>89008</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.2257522550437236</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>0.2257522550437236</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>88500</v>
+      </c>
+      <c r="C424" t="n">
+        <v>258795</v>
+      </c>
+      <c r="D424" t="n">
+        <v>90446</v>
+      </c>
+      <c r="E424" t="n">
+        <v>87737</v>
+      </c>
+      <c r="F424" t="n">
+        <v>89782</v>
+      </c>
+      <c r="G424" t="n">
+        <v>89322</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.2300764304895682</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>0.2300764304895682</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>88400</v>
+      </c>
+      <c r="C425" t="n">
+        <v>334063</v>
+      </c>
+      <c r="D425" t="n">
+        <v>90119</v>
+      </c>
+      <c r="E425" t="n">
+        <v>87765</v>
+      </c>
+      <c r="F425" t="n">
+        <v>89750</v>
+      </c>
+      <c r="G425" t="n">
+        <v>89211</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.2285478206982028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>0.2285478206982028</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>90300</v>
+      </c>
+      <c r="C426" t="n">
+        <v>200758</v>
+      </c>
+      <c r="D426" t="n">
+        <v>90121</v>
+      </c>
+      <c r="E426" t="n">
+        <v>87830</v>
+      </c>
+      <c r="F426" t="n">
+        <v>89552</v>
+      </c>
+      <c r="G426" t="n">
+        <v>89168</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.2279556565447911</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>90400</v>
+      </c>
+      <c r="C427" t="n">
+        <v>198143</v>
+      </c>
+      <c r="D427" t="n">
+        <v>90124</v>
+      </c>
+      <c r="E427" t="n">
+        <v>88047</v>
+      </c>
+      <c r="F427" t="n">
+        <v>89127</v>
+      </c>
+      <c r="G427" t="n">
+        <v>89099</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.2270054396474557</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>0.2270054396474557</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>89100</v>
+      </c>
+      <c r="C428" t="n">
+        <v>333510</v>
+      </c>
+      <c r="D428" t="n">
+        <v>89297</v>
+      </c>
+      <c r="E428" t="n">
+        <v>88242</v>
+      </c>
+      <c r="F428" t="n">
+        <v>89183</v>
+      </c>
+      <c r="G428" t="n">
+        <v>88907</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.2243613578461749</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>0.2243613578461749</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>89400</v>
+      </c>
+      <c r="C429" t="n">
+        <v>234221</v>
+      </c>
+      <c r="D429" t="n">
+        <v>89219</v>
+      </c>
+      <c r="E429" t="n">
+        <v>88307</v>
+      </c>
+      <c r="F429" t="n">
+        <v>89357</v>
+      </c>
+      <c r="G429" t="n">
+        <v>88961</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.2251050058527853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>0.2251050058527853</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>85700</v>
+      </c>
+      <c r="C430" t="n">
+        <v>378577</v>
+      </c>
+      <c r="D430" t="n">
+        <v>89130</v>
+      </c>
+      <c r="E430" t="n">
+        <v>88173</v>
+      </c>
+      <c r="F430" t="n">
+        <v>88566</v>
+      </c>
+      <c r="G430" t="n">
+        <v>88623</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.2204503201817807</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>0.2204503201817807</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>82800</v>
+      </c>
+      <c r="C431" t="n">
+        <v>429561</v>
+      </c>
+      <c r="D431" t="n">
+        <v>88621</v>
+      </c>
+      <c r="E431" t="n">
+        <v>87862</v>
+      </c>
+      <c r="F431" t="n">
+        <v>86771</v>
+      </c>
+      <c r="G431" t="n">
+        <v>87751</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.2084417820009641</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>0.2084417820009641</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>80500</v>
+      </c>
+      <c r="C432" t="n">
+        <v>358739</v>
+      </c>
+      <c r="D432" t="n">
+        <v>88193</v>
+      </c>
+      <c r="E432" t="n">
+        <v>87370</v>
+      </c>
+      <c r="F432" t="n">
+        <v>85060</v>
+      </c>
+      <c r="G432" t="n">
+        <v>86874</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.196364387523239</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>0.196364387523239</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>79600</v>
+      </c>
+      <c r="C433" t="n">
+        <v>271820</v>
+      </c>
+      <c r="D433" t="n">
+        <v>87851</v>
+      </c>
+      <c r="E433" t="n">
+        <v>86972</v>
+      </c>
+      <c r="F433" t="n">
+        <v>83367</v>
+      </c>
+      <c r="G433" t="n">
+        <v>86064</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.185209667424086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>0.185209667424086</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>76300</v>
+      </c>
+      <c r="C434" t="n">
+        <v>378445</v>
+      </c>
+      <c r="D434" t="n">
+        <v>87537</v>
+      </c>
+      <c r="E434" t="n">
+        <v>86246</v>
+      </c>
+      <c r="F434" t="n">
+        <v>81118</v>
+      </c>
+      <c r="G434" t="n">
+        <v>84967</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.1701025958823934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>0.1701025958823934</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>79000</v>
+      </c>
+      <c r="C435" t="n">
+        <v>253974</v>
+      </c>
+      <c r="D435" t="n">
+        <v>87384</v>
+      </c>
+      <c r="E435" t="n">
+        <v>85938</v>
+      </c>
+      <c r="F435" t="n">
+        <v>79775</v>
+      </c>
+      <c r="G435" t="n">
+        <v>84366</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.1618260689940094</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>0.1618260689940094</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>80300</v>
+      </c>
+      <c r="C436" t="n">
+        <v>192252</v>
+      </c>
+      <c r="D436" t="n">
+        <v>87373</v>
+      </c>
+      <c r="E436" t="n">
+        <v>85778</v>
+      </c>
+      <c r="F436" t="n">
+        <v>78951</v>
+      </c>
+      <c r="G436" t="n">
+        <v>84034</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.1572540108792948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>0.1572540108792948</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>78300</v>
+      </c>
+      <c r="C437" t="n">
+        <v>246891</v>
+      </c>
+      <c r="D437" t="n">
+        <v>86750</v>
+      </c>
+      <c r="E437" t="n">
+        <v>85439</v>
+      </c>
+      <c r="F437" t="n">
+        <v>78418</v>
+      </c>
+      <c r="G437" t="n">
+        <v>83536</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.150395923707223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>0.150395923707223</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>79400</v>
+      </c>
+      <c r="C438" t="n">
+        <v>199816</v>
+      </c>
+      <c r="D438" t="n">
+        <v>86190</v>
+      </c>
+      <c r="E438" t="n">
+        <v>85084</v>
+      </c>
+      <c r="F438" t="n">
+        <v>78320</v>
+      </c>
+      <c r="G438" t="n">
+        <v>83198</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.1457412380362184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>0.1457412380362184</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>77500</v>
+      </c>
+      <c r="C439" t="n">
+        <v>205020</v>
+      </c>
+      <c r="D439" t="n">
+        <v>86036</v>
+      </c>
+      <c r="E439" t="n">
+        <v>84320</v>
+      </c>
+      <c r="F439" t="n">
+        <v>78863</v>
+      </c>
+      <c r="G439" t="n">
+        <v>83073</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.1440198306135096</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>0.1440198306135096</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>77600</v>
+      </c>
+      <c r="C440" t="n">
+        <v>196030</v>
+      </c>
+      <c r="D440" t="n">
+        <v>85895</v>
+      </c>
+      <c r="E440" t="n">
+        <v>83432</v>
+      </c>
+      <c r="F440" t="n">
+        <v>78591</v>
+      </c>
+      <c r="G440" t="n">
+        <v>82640</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.1380568753012463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>0.1380568753012463</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>76300</v>
+      </c>
+      <c r="C441" t="n">
+        <v>220304</v>
+      </c>
+      <c r="D441" t="n">
+        <v>85486</v>
+      </c>
+      <c r="E441" t="n">
+        <v>83127</v>
+      </c>
+      <c r="F441" t="n">
+        <v>77811</v>
+      </c>
+      <c r="G441" t="n">
+        <v>82141</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.1311850168697928</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>0.1311850168697928</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>78300</v>
+      </c>
+      <c r="C442" t="n">
+        <v>326530</v>
+      </c>
+      <c r="D442" t="n">
+        <v>85196</v>
+      </c>
+      <c r="E442" t="n">
+        <v>82838</v>
+      </c>
+      <c r="F442" t="n">
+        <v>77845</v>
+      </c>
+      <c r="G442" t="n">
+        <v>81960</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.1286924189217105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>0.1286924189217105</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>81800</v>
+      </c>
+      <c r="C443" t="n">
+        <v>340659</v>
+      </c>
+      <c r="D443" t="n">
+        <v>85028</v>
+      </c>
+      <c r="E443" t="n">
+        <v>82506</v>
+      </c>
+      <c r="F443" t="n">
+        <v>78650</v>
+      </c>
+      <c r="G443" t="n">
+        <v>82061</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.1300833161192592</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>0.1300833161192592</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>83500</v>
+      </c>
+      <c r="C444" t="n">
+        <v>264998</v>
+      </c>
+      <c r="D444" t="n">
+        <v>84991</v>
+      </c>
+      <c r="E444" t="n">
+        <v>82274</v>
+      </c>
+      <c r="F444" t="n">
+        <v>79778</v>
+      </c>
+      <c r="G444" t="n">
+        <v>82348</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.1340356675617986</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성증권_일별_기준주가.xlsx
+++ b/data/삼성증권_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>0.1340356675617986</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>80400</v>
+      </c>
+      <c r="C445" t="n">
+        <v>320642</v>
+      </c>
+      <c r="D445" t="n">
+        <v>84862</v>
+      </c>
+      <c r="E445" t="n">
+        <v>81797</v>
+      </c>
+      <c r="F445" t="n">
+        <v>80203</v>
+      </c>
+      <c r="G445" t="n">
+        <v>82287</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.1331956207395166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
